--- a/QCM2_SVT.xlsx
+++ b/QCM2_SVT.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{724CB4DB-9359-448A-85E5-A887A6C1B44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34161298-C9C4-4FDF-9B6B-D0912EF37145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="QCM_Muscle" sheetId="1" r:id="rId1"/>
+    <sheet name="QCM_I.Génétique" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>

--- a/QCM2_SVT.xlsx
+++ b/QCM2_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34161298-C9C4-4FDF-9B6B-D0912EF37145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36530CE-E107-4393-989B-C35A95F737C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="158">
   <si>
     <t>Question</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>QCM Chapitre 2</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
@@ -578,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -591,6 +594,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,18 +900,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>147</v>
       </c>
@@ -931,10 +937,13 @@
         <v>154</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>156</v>
       </c>
@@ -959,8 +968,9 @@
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
@@ -985,8 +995,9 @@
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>156</v>
       </c>
@@ -1011,8 +1022,9 @@
       <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>156</v>
       </c>
@@ -1037,8 +1049,9 @@
       <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>156</v>
       </c>
@@ -1063,8 +1076,9 @@
       <c r="H6" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>156</v>
       </c>
@@ -1089,8 +1103,9 @@
       <c r="H7" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>156</v>
       </c>
@@ -1115,8 +1130,9 @@
       <c r="H8" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>156</v>
       </c>
@@ -1141,8 +1157,9 @@
       <c r="H9" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>156</v>
       </c>
@@ -1167,8 +1184,9 @@
       <c r="H10" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>156</v>
       </c>
@@ -1193,8 +1211,9 @@
       <c r="H11" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>156</v>
       </c>
@@ -1219,8 +1238,9 @@
       <c r="H12" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>156</v>
       </c>
@@ -1245,8 +1265,9 @@
       <c r="H13" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>156</v>
       </c>
@@ -1271,8 +1292,9 @@
       <c r="H14" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>156</v>
       </c>
@@ -1297,8 +1319,9 @@
       <c r="H15" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>156</v>
       </c>
@@ -1323,8 +1346,9 @@
       <c r="H16" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>156</v>
       </c>
@@ -1349,8 +1373,9 @@
       <c r="H17" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>156</v>
       </c>
@@ -1375,8 +1400,9 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>156</v>
       </c>
@@ -1401,8 +1427,9 @@
       <c r="H19" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>156</v>
       </c>
@@ -1427,8 +1454,9 @@
       <c r="H20" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>156</v>
       </c>
@@ -1453,8 +1481,9 @@
       <c r="H21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -1479,8 +1508,9 @@
       <c r="H22" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>156</v>
       </c>
@@ -1505,8 +1535,9 @@
       <c r="H23" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>156</v>
       </c>
@@ -1531,8 +1562,9 @@
       <c r="H24" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>156</v>
       </c>
@@ -1557,8 +1589,9 @@
       <c r="H25" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>156</v>
       </c>
@@ -1583,8 +1616,9 @@
       <c r="H26" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>156</v>
       </c>
@@ -1609,8 +1643,9 @@
       <c r="H27" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>156</v>
       </c>
@@ -1635,8 +1670,9 @@
       <c r="H28" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>156</v>
       </c>
@@ -1661,8 +1697,9 @@
       <c r="H29" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>156</v>
       </c>
@@ -1687,8 +1724,9 @@
       <c r="H30" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>156</v>
       </c>
@@ -1713,6 +1751,7 @@
       <c r="H31" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="I31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM2_SVT.xlsx
+++ b/QCM2_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36530CE-E107-4393-989B-C35A95F737C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE129EF-AFD8-4870-A07B-B0EDB531E6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,10 +495,10 @@
     <t>Explication</t>
   </si>
   <si>
-    <t>QCM Chapitre 2</t>
-  </si>
-  <si>
     <t>Image</t>
+  </si>
+  <si>
+    <t>TEST : Rôle du muscle strié squelettique dans la conversion de l'énergie</t>
   </si>
 </sst>
 </file>
@@ -937,15 +937,15 @@
         <v>154</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -970,9 +970,9 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -997,9 +997,9 @@
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -1024,9 +1024,9 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -1051,9 +1051,9 @@
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>21</v>
@@ -1078,9 +1078,9 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -1105,9 +1105,9 @@
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>142</v>
@@ -1132,9 +1132,9 @@
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>31</v>
@@ -1159,9 +1159,9 @@
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -1186,9 +1186,9 @@
       </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>41</v>
@@ -1213,9 +1213,9 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>46</v>
@@ -1240,9 +1240,9 @@
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>51</v>
@@ -1267,9 +1267,9 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>54</v>
@@ -1294,9 +1294,9 @@
       </c>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>58</v>
@@ -1321,9 +1321,9 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -1348,9 +1348,9 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>68</v>
@@ -1375,9 +1375,9 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>141</v>
@@ -1402,9 +1402,9 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>77</v>
@@ -1429,9 +1429,9 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>82</v>
@@ -1456,9 +1456,9 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>87</v>
@@ -1483,9 +1483,9 @@
       </c>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>91</v>
@@ -1510,9 +1510,9 @@
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>96</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="24" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>101</v>
@@ -1564,9 +1564,9 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>106</v>
@@ -1591,9 +1591,9 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>111</v>
@@ -1618,9 +1618,9 @@
       </c>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>116</v>
@@ -1645,9 +1645,9 @@
       </c>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>121</v>
@@ -1672,9 +1672,9 @@
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>126</v>
@@ -1699,9 +1699,9 @@
       </c>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>131</v>
@@ -1726,9 +1726,9 @@
       </c>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="143.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>136</v>
